--- a/docs/wireframe_document.xlsx
+++ b/docs/wireframe_document.xlsx
@@ -545,7 +545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -558,59 +558,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ドキュメント名</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>ワイヤーフレーム設計書（トップページ）</t>
+        </is>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>対象HTML</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>docs/05-wireframe.html</t>
+        </is>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>関連ページ</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>frontend/public/index.html / docs/sitemap-to-url-design.html</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ページ目的</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>忙しい飼い主に価値を短時間で伝え、LINE登録/機能閲覧へ誘導</t>
+        </is>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ターゲット</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>佐藤 美咲（32歳、ITベンチャー勤務、都市部、時間制約あり）</t>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>主要セクション</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>ヘッダー、ヒーロー、サービス紹介、提供価値バナー、ギャラリー、導入事例、実績KPI、運営情報、フッター</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -625,7 +653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -639,91 +667,156 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>16</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>レイアウト/サイズ</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>配置要素</t>
+        </is>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>12カラム相当 / コンテナ min(960px, 82vw) / セクション間余白36px</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>2カラム + 3カラムカードの組み合わせ</t>
+        </is>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ヘッダー</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>高さ56px / sticky</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>ブランド、ナビ、ログイン、お問い合わせ</t>
+        </is>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>25</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ヒーロー</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>hero-grid 1.2fr : 0.8fr / gap 24px</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>見出し、説明、CTA2種、ビジュアルカード</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>サービス紹介・主要機能</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>card-grid 3列 / gap 22px</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>健康記録、AI症状チェック、オンライン診療</t>
+        </is>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>31</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>提供価値バナー</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>1列横断（value-banner）</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>横スクロールで価値メッセージ反復表示</t>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>34</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>イメージ/導線/実績</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>image-card 3列 + 導入事例カード + stats-grid 3列</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>ギャラリー、主要機能、KPI（記録継続率/受診判断時間/対応チャネル）</t>
+        </is>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>37</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>運営情報・会社概要</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>compact-grid 2列</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>運営情報カード、会社概要カード</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>フッター</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>footer-grid</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>主要リンク、法務、運営情報</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -738,7 +831,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -752,91 +845,156 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>16</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>レイアウト/サイズ</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>配置要素</t>
+        </is>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>39</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>1カラム / 82vw / セクション間余白36px</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>縦スクロール最適化</t>
+        </is>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>41</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ヘッダー</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>高さ56px / sticky</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>ブランド、ハンバーガーメニュー</t>
+        </is>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>43</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ヒーロー</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>縦積み</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>上:見出し 中:CTA2種 下:ビジュアル</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>45</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>サービス紹介・主要機能</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>1列</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>機能カードを縦積み</t>
+        </is>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>47</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>提供価値・ギャラリー</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>1列</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>value-banner + 画像カード縦積み</t>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>49</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>導入事例・実績KPI</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>1列</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>導線カード + KPIカード縦積み</t>
+        </is>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>51</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>運営情報・会社概要</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>1列</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>2カードを縦方向表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>フッター</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1列</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>主要リンクを縦方向表示</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -851,7 +1009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -865,80 +1023,122 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>53</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>なぜその位置か</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>ユーザー効果</t>
+        </is>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>55</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ヘッダー</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>最上部固定で常時主要導線へアクセス可能にするため</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>迷子を防ぎ、相談/ログイン行動を促進</t>
+        </is>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>57</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ヒーロー</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>ファーストビューで価値とCTAを同時提示するため</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>自分向けかを短時間で判断できる</t>
+        </is>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>59</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>サービス紹介</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>興味獲得直後に機能具体化を行うため</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>理解コストを下げ、比較しやすくなる</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>61</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>機能理解後に信頼情報を提示するため</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>導入不安を軽減し意思決定を後押し</t>
+        </is>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>63</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>ヒーロー内に主要CTAを配置し即行動を促すため</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>検討から申込みへの遷移をスムーズにする</t>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>65</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>フッター</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>末尾に法務・補助導線を集約するため</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>信頼確認と最終意思決定を支援</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -953,7 +1153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -967,58 +1167,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>68</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>パス</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>71</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ワイヤーフレーム文書</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>docs/05-wireframe.html</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>トップページPC/スマホ構成を記載</t>
+        </is>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>74</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>サイトマップ統合資料</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>docs/sitemap-to-url-design.html</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>構造図・URL設計</t>
+        </is>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>77</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>トップページHTML</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>frontend/public/index.html</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>実装ソース</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>80</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>トップページ画像（PC/SP）</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>img/index.png / img/m_index.png</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>ワイヤーフレームに貼付済み</t>
+        </is>
       </c>
     </row>
   </sheetData>
